--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/006208-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/006208-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F51E17D9-52EE-4A44-93A3-975B8FE9AA72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B6D67B7-1E2E-41AD-9CDC-9D6CEAE6DFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{1997FF92-B9C3-4D58-827F-E9217BC9D1B3}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{F542B53B-3E10-4D75-BD7C-44784D19CE66}"/>
   </bookViews>
   <sheets>
     <sheet name="006208-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1484,25 +1484,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3A70DEF-33EB-4702-816F-5A4391C08D7B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49C38354-A314-42D8-A953-099300306C58}">
   <dimension ref="A1:R37"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1530,7 +1530,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1560,7 +1560,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1606,7 +1606,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1656,7 +1656,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1710,7 +1710,7 @@
         <v>3.23</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>2.38</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>26</v>
       </c>
@@ -1822,7 +1822,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="39">
         <v>2024</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>1.48</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1932,7 +1932,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>26</v>
       </c>
@@ -1988,7 +1988,7 @@
         <v>0.68</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="37">
         <v>2023</v>
       </c>
@@ -2042,7 +2042,7 @@
         <v>2.91</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>26</v>
       </c>
@@ -2098,7 +2098,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>26</v>
       </c>
@@ -2154,7 +2154,7 @@
         <v>1.77</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="39">
         <v>2022</v>
       </c>
@@ -2208,7 +2208,7 @@
         <v>3.43</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>26</v>
       </c>
@@ -2264,7 +2264,7 @@
         <v>1.57</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>26</v>
       </c>
@@ -2320,7 +2320,7 @@
         <v>1.87</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="37">
         <v>2021</v>
       </c>
@@ -2374,7 +2374,7 @@
         <v>2.41</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>26</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>26</v>
       </c>
@@ -2486,7 +2486,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <v>2020</v>
       </c>
@@ -2540,7 +2540,7 @@
         <v>2.63</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>26</v>
       </c>
@@ -2596,7 +2596,7 @@
         <v>1.77</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>26</v>
       </c>
@@ -2652,7 +2652,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="37">
         <v>2019</v>
       </c>
@@ -2706,7 +2706,7 @@
         <v>3.54</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>26</v>
       </c>
@@ -2762,7 +2762,7 @@
         <v>2.14</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>26</v>
       </c>
@@ -2818,7 +2818,7 @@
         <v>1.39</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="39">
         <v>2018</v>
       </c>
@@ -2872,7 +2872,7 @@
         <v>5.81</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
         <v>26</v>
       </c>
@@ -2928,7 +2928,7 @@
         <v>4.4800000000000004</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
         <v>26</v>
       </c>
@@ -2984,7 +2984,7 @@
         <v>1.32</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="37">
         <v>2017</v>
       </c>
@@ -3038,7 +3038,7 @@
         <v>5.42</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>26</v>
       </c>
@@ -3094,7 +3094,7 @@
         <v>3.36</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>26</v>
       </c>
@@ -3150,7 +3150,7 @@
         <v>2.06</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="39">
         <v>2016</v>
       </c>
@@ -3204,7 +3204,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="37">
         <v>2015</v>
       </c>
@@ -3258,7 +3258,7 @@
         <v>2.2599999999999998</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="39">
         <v>2014</v>
       </c>
@@ -3312,7 +3312,7 @@
         <v>3.24</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="37">
         <v>2013</v>
       </c>
@@ -3366,7 +3366,7 @@
         <v>1.91</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="39">
         <v>2012</v>
       </c>
@@ -3420,7 +3420,7 @@
         <v>6.06</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="37" t="s">
         <v>47</v>
       </c>
